--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754205</v>
       </c>
       <c r="B5" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28876-2025 artfynd.xlsx
+++ b/artfynd/A 28876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754207</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754208</v>
       </c>
       <c r="B3" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754204</v>
       </c>
       <c r="B4" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754203</v>
       </c>
       <c r="B6" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
